--- a/testing/Howler_QA_Failed_Tests_Prioritized.xlsx
+++ b/testing/Howler_QA_Failed_Tests_Prioritized.xlsx
@@ -902,7 +902,7 @@
         <v/>
       </c>
       <c r="I12" t="str">
-        <v>Fixed</v>
+        <v>Partially Fixed</v>
       </c>
     </row>
     <row r="13">
@@ -1047,7 +1047,7 @@
         <v>Cost accumulation now; also means a "delete because the image was wrong" action doesn't actually remove the image.</v>
       </c>
       <c r="I17" t="str">
-        <v>Fixed</v>
+        <v>Partially Fixed</v>
       </c>
     </row>
     <row r="18">
